--- a/output/pdf_financials_xlsx/LSTR.xlsx
+++ b/output/pdf_financials_xlsx/LSTR.xlsx
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.006727</v>
+        <v>0.035967</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.011988</v>
+        <v>0.061977</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.067236</v>
@@ -701,10 +701,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.006727</v>
+        <v>-0.035967</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.011988</v>
+        <v>-0.061977</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-3.401749</v>
@@ -738,16 +738,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.025645</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.064553</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.044557</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.017322</v>
       </c>
     </row>
     <row r="13">
@@ -1190,16 +1190,16 @@
         <v>-3.976227</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.92288</v>
+        <v>-1.948525</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-9.014329</v>
+        <v>-9.078882</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.600415</v>
+        <v>-0.644972</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.09401</v>
+        <v>-2.111332</v>
       </c>
     </row>
     <row r="28">
@@ -1246,16 +1246,16 @@
         <v>-3.976227</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.92288</v>
+        <v>-1.948525</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-9.014329</v>
+        <v>-9.078882</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.600415</v>
+        <v>-0.644972</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.09401</v>
+        <v>-2.111332</v>
       </c>
     </row>
     <row r="30">
@@ -1384,19 +1384,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.031039</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001559</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.128888</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.732167</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.295314</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.867883</v>
@@ -1440,19 +1440,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.031039</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001559</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.128888</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.732167</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.295314</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.867883</v>
@@ -1782,13 +1782,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.315726</v>
+        <v>0.186838</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.793812</v>
+        <v>0.061645</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.345343</v>
+        <v>0.050029</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.017744</v>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -14310,14 +14310,14 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>-0.035967</v>
+        <v>0.035967</v>
       </c>
       <c r="F199" s="5" t="n">
-        <v>-0.061977</v>
+        <v>0.061977</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/LSTR.xlsx
+++ b/output/pdf_financials_xlsx/LSTR.xlsx
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002119</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.002744</v>
@@ -3438,7 +3438,7 @@
         <v>0.012382</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.014517</v>
+        <v>0.012398</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.418687</v>
@@ -8439,7 +8439,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -9055,7 +9059,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
